--- a/Day6_Excel_Basics.xlsx
+++ b/Day6_Excel_Basics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.omkari\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58695294-61D5-4F82-8721-413E565B9BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE12096F-55D9-42F0-BD41-FDF3D6BF04AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
